--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="267">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -635,10 +635,6 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -688,9 +684,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://fhir.de/CodeSystem/ifa/pzn</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -808,9 +801,6 @@
   </si>
   <si>
     <t>Extension.extension:wechselwirkungserfassung_Code.value[x]:valueCodeableConcept.coding:snomed.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
   </si>
   <si>
     <t>Extension.extension:wechselwirkungserfassung_Code.value[x]:valueCodeableConcept.coding:snomed.version</t>
@@ -5041,7 +5031,7 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
@@ -5051,7 +5041,7 @@
         <v>103</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5066,18 +5056,18 @@
         <v>118</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>75</v>
@@ -5102,10 +5092,10 @@
         <v>194</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>197</v>
@@ -5160,7 +5150,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5175,15 +5165,15 @@
         <v>118</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5283,10 +5273,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5388,10 +5378,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5417,16 +5407,16 @@
         <v>106</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -5436,7 +5426,7 @@
         <v>75</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>75</v>
@@ -5475,7 +5465,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5490,15 +5480,15 @@
         <v>118</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5524,13 +5514,13 @@
         <v>85</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5580,7 +5570,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5595,15 +5585,15 @@
         <v>118</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5626,19 +5616,19 @@
         <v>151</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5687,7 +5677,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -5702,15 +5692,15 @@
         <v>118</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5736,16 +5726,16 @@
         <v>85</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -5794,7 +5784,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5809,15 +5799,15 @@
         <v>118</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5840,19 +5830,19 @@
         <v>151</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -5901,7 +5891,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5916,18 +5906,18 @@
         <v>118</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>75</v>
@@ -6010,7 +6000,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6025,15 +6015,15 @@
         <v>118</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6133,10 +6123,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6238,10 +6228,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6267,16 +6257,16 @@
         <v>106</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6286,7 +6276,7 @@
         <v>75</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>256</v>
+        <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>75</v>
@@ -6325,7 +6315,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6340,15 +6330,15 @@
         <v>118</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6374,13 +6364,13 @@
         <v>85</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6430,7 +6420,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6445,15 +6435,15 @@
         <v>118</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6476,19 +6466,19 @@
         <v>151</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -6537,7 +6527,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -6552,15 +6542,15 @@
         <v>118</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6586,16 +6576,16 @@
         <v>85</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -6644,7 +6634,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6659,15 +6649,15 @@
         <v>118</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6690,19 +6680,19 @@
         <v>151</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -6751,7 +6741,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6766,15 +6756,15 @@
         <v>118</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6800,16 +6790,16 @@
         <v>85</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -6858,7 +6848,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6873,7 +6863,7 @@
         <v>118</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -7009,7 +6999,7 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>114</v>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
+++ b/site/StructureDefinition-KBV-EX-WEST-MedicationKnowledge-Wechselwirkungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
